--- a/r4-ELGA-AustrianPatientSummary-main/observations-summary.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
   <si>
     <t>Profile</t>
   </si>
@@ -47,28 +47,43 @@
     <t>Method</t>
   </si>
   <si>
-    <t>at-ips-observationvitalsigns</t>
-  </si>
-  <si>
-    <t>AT IPS Observation Vital Signs</t>
-  </si>
-  <si>
-    <t>null#vital-signs</t>
+    <t>at-aps-observationresultslaboratorypathology</t>
+  </si>
+  <si>
+    <t>AT APS Observation Results Laboratory Pathology</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#laboratory</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-laborparameter (extensible)</t>
+  </si>
+  <si>
+    <t>dateTimeĵ, Periodĵ</t>
+  </si>
+  <si>
+    <t>CodeableConcept, stringĵ, Quantityĵ</t>
+  </si>
+  <si>
+    <t>optional</t>
+  </si>
+  <si>
+    <t>at-aps-observationvitalsigns</t>
+  </si>
+  <si>
+    <t>AT APS Observation Vital Signs</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#vital-signs</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult (extensible)</t>
   </si>
   <si>
-    <t>dateTimeĵ, Periodĵ</t>
-  </si>
-  <si>
     <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
-  </si>
-  <si>
-    <t>optional</t>
   </si>
 </sst>
 </file>
@@ -202,7 +217,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -275,6 +290,41 @@
         <v>14</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K3" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/r4-ELGA-AustrianPatientSummary-main/observations-summary.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t>Profile</t>
   </si>
@@ -47,43 +47,28 @@
     <t>Method</t>
   </si>
   <si>
-    <t>at-aps-observationresultslaboratorypathology</t>
-  </si>
-  <si>
-    <t>AT APS Observation Results Laboratory Pathology</t>
-  </si>
-  <si>
-    <t>Observation Category Codes#laboratory</t>
+    <t>at-aps-observationvitalsigns</t>
+  </si>
+  <si>
+    <t>AT APS Observation Vital Signs</t>
+  </si>
+  <si>
+    <t>null#vital-signs</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet/elga-laborparameter (extensible)</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult (extensible)</t>
   </si>
   <si>
     <t>dateTimeĵ, Periodĵ</t>
   </si>
   <si>
-    <t>CodeableConcept, stringĵ, Quantityĵ</t>
+    <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
   </si>
   <si>
     <t>optional</t>
-  </si>
-  <si>
-    <t>at-aps-observationvitalsigns</t>
-  </si>
-  <si>
-    <t>AT APS Observation Vital Signs</t>
-  </si>
-  <si>
-    <t>Observation Category Codes#vital-signs</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult (extensible)</t>
-  </si>
-  <si>
-    <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
   </si>
 </sst>
 </file>
@@ -217,7 +202,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -290,41 +275,6 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="G3" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H3" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K3" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
